--- a/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0001T0006Z000C1N31_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0001T0006Z000C1N31_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>88.00735726449557</v>
+        <v>14.30119555548053</v>
       </c>
       <c r="D2" t="n">
-        <v>86.04391083483759</v>
+        <v>13.98213551066111</v>
       </c>
       <c r="E2" t="n">
-        <v>26.26417744759325</v>
+        <v>4.267928835233904</v>
       </c>
       <c r="F2" t="n">
-        <v>25.89630659339338</v>
+        <v>4.208149821426423</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>71.04328526182672</v>
+        <v>11.54453385504684</v>
       </c>
       <c r="D3" t="n">
-        <v>69.43778445031776</v>
+        <v>11.28363997317664</v>
       </c>
       <c r="E3" t="n">
-        <v>26.26417744759325</v>
+        <v>4.267928835233904</v>
       </c>
       <c r="F3" t="n">
-        <v>25.89630659339338</v>
+        <v>4.208149821426423</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>82.44968506891421</v>
+        <v>13.39807382369856</v>
       </c>
       <c r="D4" t="n">
-        <v>80.47126288662473</v>
+        <v>13.07658021907652</v>
       </c>
       <c r="E4" t="n">
-        <v>26.26417744759325</v>
+        <v>4.267928835233904</v>
       </c>
       <c r="F4" t="n">
-        <v>25.89630659339338</v>
+        <v>4.208149821426423</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>27.01543109977709</v>
+        <v>4.390007553713778</v>
       </c>
       <c r="D5" t="n">
-        <v>27.0023733076969</v>
+        <v>4.387885662500746</v>
       </c>
       <c r="E5" t="n">
-        <v>26.26417744759325</v>
+        <v>4.267928835233904</v>
       </c>
       <c r="F5" t="n">
-        <v>25.89630659339338</v>
+        <v>4.208149821426423</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>48.10889881056646</v>
+        <v>7.817696056717049</v>
       </c>
       <c r="D6" t="n">
-        <v>46.13512479182285</v>
+        <v>7.496957778671214</v>
       </c>
       <c r="E6" t="n">
-        <v>26.26417744759325</v>
+        <v>4.267928835233904</v>
       </c>
       <c r="F6" t="n">
-        <v>25.89630659339338</v>
+        <v>4.208149821426423</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>30.40768862468702</v>
+        <v>4.941249401511641</v>
       </c>
       <c r="D7" t="n">
-        <v>28.50351639343951</v>
+        <v>4.63182141393392</v>
       </c>
       <c r="E7" t="n">
-        <v>26.26417744759325</v>
+        <v>4.267928835233904</v>
       </c>
       <c r="F7" t="n">
-        <v>25.89630659339338</v>
+        <v>4.208149821426423</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>18.28147932692136</v>
+        <v>2.970740390624722</v>
       </c>
       <c r="D8" t="n">
-        <v>17.04563358811128</v>
+        <v>2.769915458068083</v>
       </c>
       <c r="E8" t="n">
-        <v>26.26417744759325</v>
+        <v>4.267928835233904</v>
       </c>
       <c r="F8" t="n">
-        <v>25.89630659339338</v>
+        <v>4.208149821426423</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
